--- a/pls_feature_selection/results/excel_data_files/thermal_conductivity_300K_AFLOW_results.xlsx
+++ b/pls_feature_selection/results/excel_data_files/thermal_conductivity_300K_AFLOW_results.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata_and_Grid_Search" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PLS Component Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PLS Loadings (All)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PLS Loadings (Selected)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NLR Feature Selection" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata_and_Grid_Search" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLS Component Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLS Loadings (All)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLS Loadings (Selected)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NLR Feature Selection" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foldwise Selection Freq" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foldwise Runs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foldwise Summary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,1260 +552,485 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Loading Threshold</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0.1</v>
+          <t>Components tuned by CV</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>No (user-defined)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Delta R2 Threshold</t>
+          <t>Loading Threshold</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Num Selected Features</t>
+          <t>Delta R2 Threshold</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Best CV R2 Score</t>
+          <t>NLR Relative-gain Threshold</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.69196</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Best CV RMSE (orig units)</t>
+          <t>NLR Absolute Delta R2 Floor</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.56302</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GridSearch max_iter</t>
+          <t>Num Selected Features</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Num NLR-retained Features</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Best CV R2 Score</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.69196</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Best CV RMSE (orig units)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>5.59655</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>In-sample RMSE (orig units)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>5.56302</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Fold-wise check: folds</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Fold-wise check: repeats</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GridSearch max_iter</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>GridSearch tol</t>
         </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1e-08</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Grid Search CV Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>param_max_iter</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>param_tol</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>rank_test_RMSE</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>mean_test_RMSE</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>std_test_RMSE</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>mean_test_R2</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>std_test_R2</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>mean_train_RMSE</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>mean_train_R2</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>overfit_gap_R2</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>overfit_gap_RMSE</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>mean_fit_time</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>std_fit_time</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>mean_score_time</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>std_score_time</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>params</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>split0_test_R2</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="inlineStr">
-        <is>
-          <t>split1_test_R2</t>
-        </is>
-      </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>split2_test_R2</t>
-        </is>
-      </c>
-      <c r="T13" s="1" t="inlineStr">
-        <is>
-          <t>split3_test_R2</t>
-        </is>
-      </c>
-      <c r="U13" s="1" t="inlineStr">
-        <is>
-          <t>split4_test_R2</t>
-        </is>
-      </c>
-      <c r="V13" s="1" t="inlineStr">
-        <is>
-          <t>rank_test_R2</t>
-        </is>
-      </c>
-      <c r="W13" s="1" t="inlineStr">
-        <is>
-          <t>split0_train_R2</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>split1_train_R2</t>
-        </is>
-      </c>
-      <c r="Y13" s="1" t="inlineStr">
-        <is>
-          <t>split2_train_R2</t>
-        </is>
-      </c>
-      <c r="Z13" s="1" t="inlineStr">
-        <is>
-          <t>split3_train_R2</t>
-        </is>
-      </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>split4_train_R2</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>std_train_R2</t>
-        </is>
-      </c>
-      <c r="AC13" s="1" t="inlineStr">
-        <is>
-          <t>split0_test_RMSE</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>split1_test_RMSE</t>
-        </is>
-      </c>
-      <c r="AE13" s="1" t="inlineStr">
-        <is>
-          <t>split2_test_RMSE</t>
-        </is>
-      </c>
-      <c r="AF13" s="1" t="inlineStr">
-        <is>
-          <t>split3_test_RMSE</t>
-        </is>
-      </c>
-      <c r="AG13" s="1" t="inlineStr">
-        <is>
-          <t>split4_test_RMSE</t>
-        </is>
-      </c>
-      <c r="AH13" s="1" t="inlineStr">
-        <is>
-          <t>split0_train_RMSE</t>
-        </is>
-      </c>
-      <c r="AI13" s="1" t="inlineStr">
-        <is>
-          <t>split1_train_RMSE</t>
-        </is>
-      </c>
-      <c r="AJ13" s="1" t="inlineStr">
-        <is>
-          <t>split2_train_RMSE</t>
-        </is>
-      </c>
-      <c r="AK13" s="1" t="inlineStr">
-        <is>
-          <t>split3_train_RMSE</t>
-        </is>
-      </c>
-      <c r="AL13" s="1" t="inlineStr">
-        <is>
-          <t>split4_train_RMSE</t>
-        </is>
-      </c>
-      <c r="AM13" s="1" t="inlineStr">
-        <is>
-          <t>std_train_RMSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0080648899</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.000925906</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.0028190613</v>
-      </c>
-      <c r="O14" s="4" t="n">
-        <v>0.0005266851</v>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>max_iter=500, tol=1e-08</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W14" s="4" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X14" s="4" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y14" s="4" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z14" s="4" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA14" s="4" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB14" s="4" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC14" s="4" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD14" s="4" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE14" s="4" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF14" s="4" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG14" s="4" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH14" s="4" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI14" s="4" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ14" s="4" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK14" s="4" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL14" s="4" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM14" s="4" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0.008474397700000001</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0.0008453489</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0.0025001526</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0.0004537021</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=500, tol=1e-06</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y15" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z15" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA15" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB15" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC15" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD15" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF15" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG15" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH15" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI15" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ15" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK15" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL15" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM15" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0.0089920044</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0.0007039159</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>0.002542305</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0.0004927305</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=500, tol=0.0001</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y16" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z16" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA16" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB16" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC16" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD16" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE16" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF16" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG16" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH16" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI16" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ16" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK16" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL16" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM16" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>800</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1e-08</v>
       </c>
-      <c r="C17" s="2" t="n">
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Grid Search CV Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>param_max_iter</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>param_tol</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>rank_test_RMSE</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>mean_test_RMSE</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>std_test_RMSE</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>mean_test_R2</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>std_test_R2</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>mean_train_RMSE</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>mean_train_R2</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap_R2</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>overfit_gap_RMSE</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>mean_fit_time</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>std_fit_time</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>mean_score_time</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>std_score_time</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>split0_test_R2</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>split1_test_R2</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>split2_test_R2</t>
+        </is>
+      </c>
+      <c r="T20" s="1" t="inlineStr">
+        <is>
+          <t>split3_test_R2</t>
+        </is>
+      </c>
+      <c r="U20" s="1" t="inlineStr">
+        <is>
+          <t>split4_test_R2</t>
+        </is>
+      </c>
+      <c r="V20" s="1" t="inlineStr">
+        <is>
+          <t>rank_test_R2</t>
+        </is>
+      </c>
+      <c r="W20" s="1" t="inlineStr">
+        <is>
+          <t>split0_train_R2</t>
+        </is>
+      </c>
+      <c r="X20" s="1" t="inlineStr">
+        <is>
+          <t>split1_train_R2</t>
+        </is>
+      </c>
+      <c r="Y20" s="1" t="inlineStr">
+        <is>
+          <t>split2_train_R2</t>
+        </is>
+      </c>
+      <c r="Z20" s="1" t="inlineStr">
+        <is>
+          <t>split3_train_R2</t>
+        </is>
+      </c>
+      <c r="AA20" s="1" t="inlineStr">
+        <is>
+          <t>split4_train_R2</t>
+        </is>
+      </c>
+      <c r="AB20" s="1" t="inlineStr">
+        <is>
+          <t>std_train_R2</t>
+        </is>
+      </c>
+      <c r="AC20" s="1" t="inlineStr">
+        <is>
+          <t>split0_test_RMSE</t>
+        </is>
+      </c>
+      <c r="AD20" s="1" t="inlineStr">
+        <is>
+          <t>split1_test_RMSE</t>
+        </is>
+      </c>
+      <c r="AE20" s="1" t="inlineStr">
+        <is>
+          <t>split2_test_RMSE</t>
+        </is>
+      </c>
+      <c r="AF20" s="1" t="inlineStr">
+        <is>
+          <t>split3_test_RMSE</t>
+        </is>
+      </c>
+      <c r="AG20" s="1" t="inlineStr">
+        <is>
+          <t>split4_test_RMSE</t>
+        </is>
+      </c>
+      <c r="AH20" s="1" t="inlineStr">
+        <is>
+          <t>split0_train_RMSE</t>
+        </is>
+      </c>
+      <c r="AI20" s="1" t="inlineStr">
+        <is>
+          <t>split1_train_RMSE</t>
+        </is>
+      </c>
+      <c r="AJ20" s="1" t="inlineStr">
+        <is>
+          <t>split2_train_RMSE</t>
+        </is>
+      </c>
+      <c r="AK20" s="1" t="inlineStr">
+        <is>
+          <t>split3_train_RMSE</t>
+        </is>
+      </c>
+      <c r="AL20" s="1" t="inlineStr">
+        <is>
+          <t>split4_train_RMSE</t>
+        </is>
+      </c>
+      <c r="AM20" s="1" t="inlineStr">
+        <is>
+          <t>std_train_RMSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="D21" s="4" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F21" s="4" t="n">
         <v>0.6919611277</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.0280712295</v>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I17" s="2" t="n">
+      <c r="H21" s="4" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>0.6974385003</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J21" s="4" t="n">
         <v>0.0054773726</v>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0.0088476658</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>0.0008863334</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>0.0021803856</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0.0004122197</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=800, tol=1e-08</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="n">
+      <c r="K21" s="4" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.0064173222</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.0011653199</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0.0017082214</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0.0003968488</v>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>max_iter=500, tol=1e-08</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>0.6645567307</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="R21" s="4" t="n">
         <v>0.7234547958000001</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="S21" s="4" t="n">
         <v>0.7155840474</v>
       </c>
-      <c r="T17" s="2" t="n">
+      <c r="T21" s="4" t="n">
         <v>0.6530541596</v>
       </c>
-      <c r="U17" s="2" t="n">
+      <c r="U21" s="4" t="n">
         <v>0.7031559047</v>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="V21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="W21" s="4" t="n">
         <v>0.7044498128</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="X21" s="4" t="n">
         <v>0.6858190625</v>
       </c>
-      <c r="Y17" s="2" t="n">
+      <c r="Y21" s="4" t="n">
         <v>0.6943214759</v>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="Z21" s="4" t="n">
         <v>0.7068828469</v>
       </c>
-      <c r="AA17" s="2" t="n">
+      <c r="AA21" s="4" t="n">
         <v>0.6957193033</v>
       </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AB21" s="4" t="n">
         <v>0.0075635574</v>
       </c>
-      <c r="AC17" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD17" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE17" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF17" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG17" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH17" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI17" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ17" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK17" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL17" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM17" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0.007976388900000001</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>0.000705272</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>0.0025084496</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>0.0006396339</v>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=800, tol=1e-06</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W18" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X18" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y18" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z18" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA18" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB18" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC18" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD18" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE18" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF18" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG18" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH18" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI18" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ18" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK18" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL18" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM18" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J19" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0.008175373099999999</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>0.000386995</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>0.0022064209</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>0.0002555897</v>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=800, tol=0.0001</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R19" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S19" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X19" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y19" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z19" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA19" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB19" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC19" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD19" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE19" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF19" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG19" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH19" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI19" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ19" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK19" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL19" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM19" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0.0085757256</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0.0001838742</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>0.0027644634</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>0.0005063639</v>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=1000, tol=1e-08</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S20" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T20" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X20" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y20" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z20" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA20" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB20" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC20" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD20" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG20" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH20" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI20" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ20" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK20" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL20" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM20" s="2" t="n">
-        <v>0.006667974</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>-0.5535203356</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.0260600763</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0.6919611277</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0.0280712295</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>-0.5499476334</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0.6974385003</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0.0054773726</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>-0.0035727022</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0.008470916699999999</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>0.0005158841</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>0.0028696537</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>0.0005414912</v>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>max_iter=1000, tol=1e-06</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>0.6645567307</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>0.7234547958000001</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>0.7155840474</v>
-      </c>
-      <c r="T21" s="2" t="n">
-        <v>0.6530541596</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>0.7031559047</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="2" t="n">
-        <v>0.7044498128</v>
-      </c>
-      <c r="X21" s="2" t="n">
-        <v>0.6858190625</v>
-      </c>
-      <c r="Y21" s="2" t="n">
-        <v>0.6943214759</v>
-      </c>
-      <c r="Z21" s="2" t="n">
-        <v>0.7068828469</v>
-      </c>
-      <c r="AA21" s="2" t="n">
-        <v>0.6957193033</v>
-      </c>
-      <c r="AB21" s="2" t="n">
-        <v>0.0075635574</v>
-      </c>
-      <c r="AC21" s="2" t="n">
-        <v>-0.5550840183</v>
-      </c>
-      <c r="AD21" s="2" t="n">
-        <v>-0.5397053094000001</v>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>-0.5117768359</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>-0.5794939078</v>
-      </c>
-      <c r="AG21" s="2" t="n">
-        <v>-0.5815416063</v>
-      </c>
-      <c r="AH21" s="2" t="n">
-        <v>-0.5491569216</v>
-      </c>
-      <c r="AI21" s="2" t="n">
-        <v>-0.5567694052</v>
-      </c>
-      <c r="AJ21" s="2" t="n">
-        <v>-0.5583193943</v>
-      </c>
-      <c r="AK21" s="2" t="n">
-        <v>-0.5435649352</v>
-      </c>
-      <c r="AL21" s="2" t="n">
-        <v>-0.5419275105</v>
-      </c>
-      <c r="AM21" s="2" t="n">
-        <v>0.006667974</v>
+      <c r="AC21" s="4" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD21" s="4" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE21" s="4" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF21" s="4" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG21" s="4" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH21" s="4" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI21" s="4" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ21" s="4" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK21" s="4" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL21" s="4" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM21" s="4" t="n">
+        <v>0.0674187965</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.0001</v>
+        <v>1e-06</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>-0.5535203356</v>
+        <v>-5.5965537821</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.0260600763</v>
+        <v>0.2634891787</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.6919611277</v>
@@ -1811,7 +1039,7 @@
         <v>0.0280712295</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>-0.5499476334</v>
+        <v>-5.5604307729</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0.6974385003</v>
@@ -1820,23 +1048,23 @@
         <v>0.0054773726</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-0.0035727022</v>
+        <v>-0.0361230092</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.0101821423</v>
+        <v>0.0056035519</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.0040486968</v>
+        <v>0.0007969279</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0026862621</v>
+        <v>0.0014431</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.000915903</v>
+        <v>0.0005478374</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>max_iter=1000, tol=0.0001</t>
+          <t>max_iter=500, tol=1e-06</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n">
@@ -1876,54 +1104,54 @@
         <v>0.0075635574</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>-0.5550840183</v>
+        <v>-5.6123639234</v>
       </c>
       <c r="AD22" s="2" t="n">
-        <v>-0.5397053094000001</v>
+        <v>-5.4568723073</v>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>-0.5117768359</v>
+        <v>-5.1744920695</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>-0.5794939078</v>
+        <v>-5.8591683324</v>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>-0.5815416063</v>
+        <v>-5.8798722779</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>-0.5491569216</v>
+        <v>-5.5524360156</v>
       </c>
       <c r="AI22" s="2" t="n">
-        <v>-0.5567694052</v>
+        <v>-5.6294045949</v>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>-0.5583193943</v>
+        <v>-5.6450762812</v>
       </c>
       <c r="AK22" s="2" t="n">
-        <v>-0.5435649352</v>
+        <v>-5.4958963534</v>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>-0.5419275105</v>
+        <v>-5.4793406195</v>
       </c>
       <c r="AM22" s="2" t="n">
-        <v>0.006667974</v>
+        <v>0.0674187965</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1e-08</v>
+        <v>0.0001</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>-0.5535203356</v>
+        <v>-5.5965537821</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.0260600763</v>
+        <v>0.2634891787</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.6919611277</v>
@@ -1932,7 +1160,7 @@
         <v>0.0280712295</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>-0.5499476334</v>
+        <v>-5.5604307729</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0.6974385003</v>
@@ -1941,23 +1169,23 @@
         <v>0.0054773726</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-0.0035727022</v>
+        <v>-0.0361230092</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.0119760036</v>
+        <v>0.0056065083</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.0029840615</v>
+        <v>0.0011913414</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.002855587</v>
+        <v>0.0016001701</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.0005151535</v>
+        <v>0.0008003235</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>max_iter=2000, tol=1e-08</t>
+          <t>max_iter=500, tol=0.0001</t>
         </is>
       </c>
       <c r="Q23" s="2" t="n">
@@ -1997,54 +1225,54 @@
         <v>0.0075635574</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>-0.5550840183</v>
+        <v>-5.6123639234</v>
       </c>
       <c r="AD23" s="2" t="n">
-        <v>-0.5397053094000001</v>
+        <v>-5.4568723073</v>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>-0.5117768359</v>
+        <v>-5.1744920695</v>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>-0.5794939078</v>
+        <v>-5.8591683324</v>
       </c>
       <c r="AG23" s="2" t="n">
-        <v>-0.5815416063</v>
+        <v>-5.8798722779</v>
       </c>
       <c r="AH23" s="2" t="n">
-        <v>-0.5491569216</v>
+        <v>-5.5524360156</v>
       </c>
       <c r="AI23" s="2" t="n">
-        <v>-0.5567694052</v>
+        <v>-5.6294045949</v>
       </c>
       <c r="AJ23" s="2" t="n">
-        <v>-0.5583193943</v>
+        <v>-5.6450762812</v>
       </c>
       <c r="AK23" s="2" t="n">
-        <v>-0.5435649352</v>
+        <v>-5.4958963534</v>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>-0.5419275105</v>
+        <v>-5.4793406195</v>
       </c>
       <c r="AM23" s="2" t="n">
-        <v>0.006667974</v>
+        <v>0.0674187965</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-08</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>-0.5535203356</v>
+        <v>-5.5965537821</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.0260600763</v>
+        <v>0.2634891787</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0.6919611277</v>
@@ -2053,7 +1281,7 @@
         <v>0.0280712295</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>-0.5499476334</v>
+        <v>-5.5604307729</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0.6974385003</v>
@@ -2062,23 +1290,23 @@
         <v>0.0054773726</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-0.0035727022</v>
+        <v>-0.0361230092</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.0085152149</v>
+        <v>0.0059179306</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.0010545827</v>
+        <v>0.0013552767</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0025646687</v>
+        <v>0.0018089771</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.0004655999</v>
+        <v>0.0004048541</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>max_iter=2000, tol=1e-06</t>
+          <t>max_iter=800, tol=1e-08</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n">
@@ -2118,54 +1346,54 @@
         <v>0.0075635574</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>-0.5550840183</v>
+        <v>-5.6123639234</v>
       </c>
       <c r="AD24" s="2" t="n">
-        <v>-0.5397053094000001</v>
+        <v>-5.4568723073</v>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>-0.5117768359</v>
+        <v>-5.1744920695</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>-0.5794939078</v>
+        <v>-5.8591683324</v>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>-0.5815416063</v>
+        <v>-5.8798722779</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>-0.5491569216</v>
+        <v>-5.5524360156</v>
       </c>
       <c r="AI24" s="2" t="n">
-        <v>-0.5567694052</v>
+        <v>-5.6294045949</v>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>-0.5583193943</v>
+        <v>-5.6450762812</v>
       </c>
       <c r="AK24" s="2" t="n">
-        <v>-0.5435649352</v>
+        <v>-5.4958963534</v>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>-0.5419275105</v>
+        <v>-5.4793406195</v>
       </c>
       <c r="AM24" s="2" t="n">
-        <v>0.006667974</v>
+        <v>0.0674187965</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.0001</v>
+        <v>1e-06</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>-0.5535203356</v>
+        <v>-5.5965537821</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.0260600763</v>
+        <v>0.2634891787</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0.6919611277</v>
@@ -2174,7 +1402,7 @@
         <v>0.0280712295</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>-0.5499476334</v>
+        <v>-5.5604307729</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0.6974385003</v>
@@ -2183,23 +1411,23 @@
         <v>0.0054773726</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-0.0035727022</v>
+        <v>-0.0361230092</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0.0073771954</v>
+        <v>0.0059305668</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.0009986867</v>
+        <v>0.0010823247</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0028436661</v>
+        <v>0.0018376827</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.0005303742</v>
+        <v>0.0007578527</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>max_iter=2000, tol=0.0001</t>
+          <t>max_iter=800, tol=1e-06</t>
         </is>
       </c>
       <c r="Q25" s="2" t="n">
@@ -2239,37 +1467,884 @@
         <v>0.0075635574</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>-0.5550840183</v>
+        <v>-5.6123639234</v>
       </c>
       <c r="AD25" s="2" t="n">
-        <v>-0.5397053094000001</v>
+        <v>-5.4568723073</v>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>-0.5117768359</v>
+        <v>-5.1744920695</v>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>-0.5794939078</v>
+        <v>-5.8591683324</v>
       </c>
       <c r="AG25" s="2" t="n">
-        <v>-0.5815416063</v>
+        <v>-5.8798722779</v>
       </c>
       <c r="AH25" s="2" t="n">
-        <v>-0.5491569216</v>
+        <v>-5.5524360156</v>
       </c>
       <c r="AI25" s="2" t="n">
-        <v>-0.5567694052</v>
+        <v>-5.6294045949</v>
       </c>
       <c r="AJ25" s="2" t="n">
-        <v>-0.5583193943</v>
+        <v>-5.6450762812</v>
       </c>
       <c r="AK25" s="2" t="n">
-        <v>-0.5435649352</v>
+        <v>-5.4958963534</v>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>-0.5419275105</v>
+        <v>-5.4793406195</v>
       </c>
       <c r="AM25" s="2" t="n">
-        <v>0.006667974</v>
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.0055323124</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0.0008598571</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.0012016296</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.0004000774</v>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=800, tol=0.0001</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0.0052005291</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0.0009792032</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0.0014043331</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.0004954192</v>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=1000, tol=1e-08</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD27" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI27" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ27" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.0048013687</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.0003991616</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.0012426376</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.0003924367</v>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=1000, tol=1e-06</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI28" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ28" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0.0052477837</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0.0014666634</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.0014079571</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.0004991657</v>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=1000, tol=0.0001</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI29" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ29" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.0072366714</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0.0002887347</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.001608181</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0.0004967188</v>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=2000, tol=1e-08</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI30" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0.006513834</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0.0012746166</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.0015995026</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0.0004896489</v>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=2000, tol=1e-06</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI31" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ31" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>0.0674187965</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-5.5965537821</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.2634891787</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.6919611277</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.0280712295</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>-5.5604307729</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.6974385003</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.0054773726</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>-0.0361230092</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0.0065940857</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0.0008912116</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.0020062447</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>7.8053e-06</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>max_iter=2000, tol=0.0001</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.6645567307</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.7234547958000001</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0.7155840474</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0.6530541596</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0.7031559047</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0.7044498128</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0.6858190625</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>0.6943214759</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>0.7068828469</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>0.6957193033</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0.0075635574</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>-5.6123639234</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>-5.4568723073</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>-5.1744920695</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>-5.8591683324</v>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>-5.8798722779</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>-5.5524360156</v>
+      </c>
+      <c r="AI32" s="2" t="n">
+        <v>-5.6294045949</v>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>-5.6450762812</v>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>-5.4958963534</v>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>-5.4793406195</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>0.0674187965</v>
       </c>
     </row>
   </sheetData>
@@ -3030,13 +3105,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3060,6 +3137,16 @@
           <t>NLR Delta R2</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NLR Relative Gain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Retained</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -3076,6 +3163,14 @@
       <c r="D2" s="2" t="n">
         <v>0.572585</v>
       </c>
+      <c r="E2" s="2" t="n">
+        <v>0.572585</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -3092,6 +3187,14 @@
       <c r="D3" s="2" t="n">
         <v>0.05989</v>
       </c>
+      <c r="E3" s="2" t="n">
+        <v>0.14012</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -3107,6 +3210,14 @@
       </c>
       <c r="D4" s="2" t="n">
         <v>0.002568</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.006987</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3124,6 +3235,14 @@
       <c r="D5" s="2" t="n">
         <v>0.003664</v>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>0.010038</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -3135,10 +3254,18 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.638697</v>
+        <v>0.638696</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-9e-06</v>
+        <v>-1.1e-05</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>-2.9e-05</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3154,7 +3281,15 @@
         <v>0.640518</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.001821</v>
+        <v>0.001823</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.005045</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3167,10 +3302,18 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.6454220000000001</v>
+        <v>0.645423</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.004904</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.013643</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3188,6 +3331,14 @@
       <c r="D9" s="2" t="n">
         <v>0.001199</v>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -3204,6 +3355,14 @@
       <c r="D10" s="2" t="n">
         <v>2.6e-05</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>7.3e-05</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -3218,7 +3377,15 @@
         <v>0.717295</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.070649</v>
+        <v>0.070648</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.199936</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3236,6 +3403,14 @@
       <c r="D12" s="2" t="n">
         <v>0.009757999999999999</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>0.034517</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -3247,10 +3422,18 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.73978</v>
+        <v>0.739779</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.012726</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.046626</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3267,6 +3450,2567 @@
       </c>
       <c r="D14" s="2" t="n">
         <v>8.3e-05</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.000318</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PLS-screened frequency</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>NLR-retained frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PLS-screened (n of runs)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NLR-retained (n of runs)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mean PLS rank (when screened)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>In full-data retained set</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>YM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>EPA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ENPA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>VPA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ANI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PUGR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IPUGR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ASPIN</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BGAP</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fold</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>N train</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N test</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Selected PLS components</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PLS-screened features</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NLR-retained features</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>N retained</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Held-out R2 (retained set)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Held-out RMSE (retained set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.672453</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>5.545915</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PR, PUGR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.754872</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>5.137562</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.699626</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>5.317678</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.674219</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>5.677638</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.705932</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>5.852318</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.74369</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>5.134021</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA, D</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.674467</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>5.547986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.703168</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>5.582986</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.701322</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>5.203452</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0.69914</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>5.959765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.685534</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>5.866156</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.68384</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>5.55985</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.690669</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>5.515557</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0.716923</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>4.907171</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PR, PUGR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.735596</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>5.63596</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0.657925</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>5.891679</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.7756</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>5.158824</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.704472</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>5.569512</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.701881</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>5.012452</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.662286</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>5.857185</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0.684599</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>5.451053</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0.6494180000000001</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>5.753024</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA, D</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0.68646</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>5.55302</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PR, PUGR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0.771364</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>5.183285</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0.711964</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>5.54035</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0.6767879999999999</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>6.05123</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0.74565</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>5.765058</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0.654769</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>4.802788</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0.708646</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>5.15103</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA, D</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0.707203</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>5.640154</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PR, PUGR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.715684</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>6.335416</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0.726699</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>4.916264</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0.671018</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>4.772791</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0.682254</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>5.740442</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.699331</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>5.705612</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA, D</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0.674377</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>5.383758</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0.67786</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>5.80559</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0.6962120000000001</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>5.409399</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PR, PUGR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0.745301</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>5.994145</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>0.7047060000000001</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>4.854076</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.729264</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>5.118626</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0.73228</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>5.89334</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.65727</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>5.317064</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0.7013239999999999</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>5.535623</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA, D</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.6802</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>5.630357</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0.658374</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>6.651606</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4061</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.697157</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>5.282802</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI, ASPIN</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0.765498</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>4.924936</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0.698414</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>5.401739</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>4062</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>PLS1, PLS2</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, BM, EPA, ENPA, VPA, PUGR, PR, IPUGR, NA, NE, D, ANI</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0.701311</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>5.150914</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total fold-wise runs</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Full-data NLR-retained set</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM, YM, NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Runs retaining exactly the full-data set</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Fraction retaining exactly the full-data set</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Held-out R2 (retained set): mean</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.7010999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Held-out R2 (retained set): std</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.030818</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Held-out R2 (retained set): min</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.6494180000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Held-out R2 (retained set): max</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.7756</v>
       </c>
     </row>
   </sheetData>
